--- a/input/timetable/Электроэнергетика.xlsx
+++ b/input/timetable/Электроэнергетика.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="159">
   <si>
     <t>пара</t>
   </si>
@@ -242,9 +242,6 @@
     <t>Физика, п/г 1, А316//</t>
   </si>
   <si>
-    <t>Электр. машины, п/г 1, У206// Электрические машины (пр), У307</t>
-  </si>
-  <si>
     <t>Инж. и комп. графика, п/г 2, У304</t>
   </si>
   <si>
@@ -338,9 +335,6 @@
     <t>Электромагнитные поля и волны (пр), У305</t>
   </si>
   <si>
-    <t>Электрические машины (пр), У307//Электр машины, п/г 2, У206</t>
-  </si>
-  <si>
     <t>Ремонт и обсл. электр. аппаратов и оборудования, п/г 2, У306</t>
   </si>
   <si>
@@ -380,9 +374,6 @@
     <t>// Безопасность жизнедеятельности (пр), А414</t>
   </si>
   <si>
-    <t>Электрические машины (лек), У902</t>
-  </si>
-  <si>
     <t>Иностранный язык, п/г 2, А518</t>
   </si>
   <si>
@@ -504,6 +495,15 @@
   </si>
   <si>
     <t>Физика (лек), А436</t>
+  </si>
+  <si>
+    <t>Электрические машины (лек), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>//Электрические машины (пр), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Электрические машины (пр), ЭОиДОТ//</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1443,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="295">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1922,8 +1922,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2004,9 +2002,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2193,18 +2188,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2582,7 +2568,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>69</v>
@@ -2592,7 +2578,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
       <c r="L4" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -2600,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -2613,7 +2599,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="10" t="s">
@@ -2660,7 +2646,7 @@
       </c>
       <c r="D7" s="134"/>
       <c r="E7" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
@@ -2673,7 +2659,7 @@
       </c>
       <c r="J7" s="134"/>
       <c r="K7" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>7</v>
@@ -2684,7 +2670,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="135" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" s="135"/>
       <c r="E8" s="135"/>
@@ -2693,7 +2679,7 @@
         <v>26</v>
       </c>
       <c r="I8" s="135" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J8" s="135"/>
       <c r="K8" s="135"/>
@@ -2753,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="95" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" s="96"/>
       <c r="E11" s="96"/>
@@ -2763,7 +2749,7 @@
         <v>3</v>
       </c>
       <c r="I11" s="95" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J11" s="96"/>
       <c r="K11" s="96"/>
@@ -2775,11 +2761,11 @@
         <v>4</v>
       </c>
       <c r="C12" s="95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" s="96"/>
       <c r="E12" s="96" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F12" s="97"/>
       <c r="G12" s="25"/>
@@ -2799,11 +2785,11 @@
         <v>5</v>
       </c>
       <c r="C13" s="110" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D13" s="111"/>
       <c r="E13" s="111" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13" s="112"/>
       <c r="G13" s="25"/>
@@ -2823,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" s="89"/>
       <c r="E14" s="90"/>
@@ -2845,7 +2831,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="85" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D15" s="86"/>
       <c r="E15" s="86"/>
@@ -2855,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="85" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J15" s="86"/>
       <c r="K15" s="86"/>
@@ -2867,7 +2853,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="98" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" s="99"/>
       <c r="E16" s="99"/>
@@ -2877,7 +2863,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J16" s="86"/>
       <c r="K16" s="86"/>
@@ -2939,7 +2925,7 @@
       <c r="I19" s="95"/>
       <c r="J19" s="96"/>
       <c r="K19" s="96" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L19" s="97"/>
     </row>
@@ -2971,7 +2957,7 @@
         <v>6</v>
       </c>
       <c r="C21" s="157" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21" s="158"/>
       <c r="E21" s="158"/>
@@ -2981,7 +2967,7 @@
         <v>6</v>
       </c>
       <c r="I21" s="160" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J21" s="161"/>
       <c r="K21" s="161"/>
@@ -3005,7 +2991,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="154" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J22" s="155"/>
       <c r="K22" s="155"/>
@@ -3017,7 +3003,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D23" s="96"/>
       <c r="E23" s="96"/>
@@ -3027,7 +3013,7 @@
         <v>3</v>
       </c>
       <c r="I23" s="95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J23" s="96"/>
       <c r="K23" s="96"/>
@@ -3039,7 +3025,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" s="99"/>
       <c r="E24" s="99"/>
@@ -3049,11 +3035,11 @@
         <v>4</v>
       </c>
       <c r="I24" s="95" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J24" s="96"/>
       <c r="K24" s="96" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L24" s="97"/>
     </row>
@@ -3065,7 +3051,7 @@
       <c r="C25" s="168"/>
       <c r="D25" s="169"/>
       <c r="E25" s="170" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F25" s="159"/>
       <c r="G25" s="29"/>
@@ -3073,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="I25" s="110" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J25" s="111"/>
       <c r="K25" s="163"/>
@@ -3132,7 +3118,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="118" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" s="119"/>
       <c r="E28" s="119"/>
@@ -3142,7 +3128,7 @@
         <v>3</v>
       </c>
       <c r="I28" s="98" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J28" s="99"/>
       <c r="K28" s="99"/>
@@ -3154,7 +3140,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="98" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D29" s="99"/>
       <c r="E29" s="99"/>
@@ -3164,7 +3150,7 @@
         <v>4</v>
       </c>
       <c r="I29" s="95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J29" s="96"/>
       <c r="K29" s="96"/>
@@ -3186,7 +3172,7 @@
       </c>
       <c r="J30" s="131"/>
       <c r="K30" s="132" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L30" s="133"/>
     </row>
@@ -3222,7 +3208,7 @@
       </c>
       <c r="D32" s="131"/>
       <c r="E32" s="132" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F32" s="133"/>
       <c r="G32" s="33"/>
@@ -3252,7 +3238,7 @@
       <c r="I33" s="113"/>
       <c r="J33" s="114"/>
       <c r="K33" s="96" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L33" s="97"/>
     </row>
@@ -3296,7 +3282,7 @@
         <v>30</v>
       </c>
       <c r="C36" s="115" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D36" s="116"/>
       <c r="E36" s="116"/>
@@ -3306,7 +3292,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="115" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J36" s="116"/>
       <c r="K36" s="116"/>
@@ -3556,7 +3542,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>69</v>
@@ -3566,7 +3552,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
       <c r="L4" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -3574,7 +3560,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -3587,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="10" t="s">
@@ -3658,7 +3644,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="135" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" s="135"/>
       <c r="E8" s="135"/>
@@ -3667,7 +3653,7 @@
         <v>26</v>
       </c>
       <c r="I8" s="135" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J8" s="135"/>
       <c r="K8" s="135"/>
@@ -3706,42 +3692,42 @@
       <c r="B10" s="28">
         <v>1</v>
       </c>
-      <c r="C10" s="205" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="206"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="207"/>
+      <c r="C10" s="203" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="204"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="205"/>
       <c r="G10" s="23" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="28">
         <v>1</v>
       </c>
-      <c r="I10" s="205" t="s">
-        <v>108</v>
-      </c>
-      <c r="J10" s="206"/>
-      <c r="K10" s="206"/>
-      <c r="L10" s="207"/>
+      <c r="I10" s="203" t="s">
+        <v>106</v>
+      </c>
+      <c r="J10" s="204"/>
+      <c r="K10" s="204"/>
+      <c r="L10" s="205"/>
     </row>
     <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="25"/>
       <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="206" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="209"/>
-      <c r="E11" s="209"/>
-      <c r="F11" s="210"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="208"/>
       <c r="G11" s="25"/>
       <c r="H11" s="26">
         <v>2</v>
       </c>
       <c r="I11" s="95" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J11" s="96"/>
       <c r="K11" s="96"/>
@@ -3765,7 +3751,7 @@
       </c>
       <c r="J12" s="86"/>
       <c r="K12" s="86" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L12" s="87"/>
     </row>
@@ -3800,20 +3786,20 @@
       </c>
       <c r="C14" s="183"/>
       <c r="D14" s="184"/>
-      <c r="E14" s="231" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="232"/>
+      <c r="E14" s="226" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="227"/>
       <c r="G14" s="27" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="28">
         <v>1</v>
       </c>
-      <c r="I14" s="237"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238"/>
-      <c r="L14" s="239"/>
+      <c r="I14" s="232"/>
+      <c r="J14" s="233"/>
+      <c r="K14" s="233"/>
+      <c r="L14" s="234"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="25"/>
@@ -3843,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="95" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D16" s="96"/>
       <c r="E16" s="96"/>
@@ -3853,7 +3839,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="95" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J16" s="96"/>
       <c r="K16" s="96"/>
@@ -3884,80 +3870,86 @@
       <c r="B18" s="28">
         <v>1</v>
       </c>
-      <c r="C18" s="240" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="242"/>
+      <c r="C18" s="235" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="236"/>
+      <c r="E18" s="236"/>
+      <c r="F18" s="237"/>
       <c r="G18" s="27" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="28">
         <v>1</v>
       </c>
-      <c r="I18" s="194" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="243"/>
-      <c r="K18" s="243"/>
-      <c r="L18" s="197"/>
+      <c r="I18" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" s="238"/>
+      <c r="K18" s="238"/>
+      <c r="L18" s="195"/>
     </row>
     <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="25"/>
-      <c r="B19" s="26">
-        <v>2</v>
-      </c>
-      <c r="C19" s="215"/>
-      <c r="D19" s="216"/>
-      <c r="E19" s="216"/>
-      <c r="F19" s="217"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="213"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="214"/>
+      <c r="F19" s="215"/>
       <c r="G19" s="25"/>
       <c r="H19" s="26">
         <v>2</v>
       </c>
       <c r="I19" s="98" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J19" s="171"/>
-      <c r="K19" s="236"/>
+      <c r="K19" s="231"/>
       <c r="L19" s="84"/>
     </row>
     <row r="20" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="42"/>
       <c r="B20" s="43">
-        <v>3</v>
-      </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
+        <v>4</v>
+      </c>
+      <c r="C20" s="98" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="100"/>
       <c r="G20" s="42"/>
       <c r="H20" s="43">
-        <v>3</v>
-      </c>
-      <c r="I20" s="202"/>
-      <c r="J20" s="203"/>
-      <c r="K20" s="192"/>
-      <c r="L20" s="193"/>
+        <v>4</v>
+      </c>
+      <c r="I20" s="98" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" s="99"/>
+      <c r="K20" s="99"/>
+      <c r="L20" s="100"/>
     </row>
     <row r="21" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="29"/>
       <c r="B21" s="30">
-        <v>4</v>
-      </c>
-      <c r="C21" s="92"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="94"/>
+        <v>5</v>
+      </c>
+      <c r="C21" s="160" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="162"/>
       <c r="G21" s="29"/>
       <c r="H21" s="30">
-        <v>4</v>
-      </c>
-      <c r="I21" s="228"/>
-      <c r="J21" s="229"/>
-      <c r="K21" s="229"/>
-      <c r="L21" s="230"/>
+        <v>5</v>
+      </c>
+      <c r="I21" s="157" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="158"/>
+      <c r="K21" s="158"/>
+      <c r="L21" s="159"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="27" t="s">
@@ -3966,26 +3958,26 @@
       <c r="B22" s="28">
         <v>1</v>
       </c>
-      <c r="C22" s="194" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="195"/>
-      <c r="E22" s="196" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="197"/>
+      <c r="C22" s="192" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="193"/>
+      <c r="E22" s="194" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="195"/>
       <c r="G22" s="27" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="28">
         <v>1</v>
       </c>
-      <c r="I22" s="233" t="s">
-        <v>102</v>
-      </c>
-      <c r="J22" s="234"/>
-      <c r="K22" s="234"/>
-      <c r="L22" s="235"/>
+      <c r="I22" s="228" t="s">
+        <v>101</v>
+      </c>
+      <c r="J22" s="229"/>
+      <c r="K22" s="229"/>
+      <c r="L22" s="230"/>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="25"/>
@@ -3993,7 +3985,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" s="99"/>
       <c r="E23" s="99"/>
@@ -4002,24 +3994,24 @@
       <c r="H23" s="26">
         <v>2</v>
       </c>
-      <c r="I23" s="202"/>
-      <c r="J23" s="203"/>
-      <c r="K23" s="203" t="s">
-        <v>72</v>
-      </c>
-      <c r="L23" s="204"/>
+      <c r="I23" s="200"/>
+      <c r="J23" s="201"/>
+      <c r="K23" s="201" t="s">
+        <v>71</v>
+      </c>
+      <c r="L23" s="202"/>
     </row>
     <row r="24" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="215" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" s="216"/>
-      <c r="E24" s="216"/>
-      <c r="F24" s="217"/>
+      <c r="C24" s="213" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="214"/>
+      <c r="E24" s="214"/>
+      <c r="F24" s="215"/>
       <c r="G24" s="25"/>
       <c r="H24" s="26">
         <v>3</v>
@@ -4063,7 +4055,7 @@
       </c>
       <c r="D26" s="86"/>
       <c r="E26" s="96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F26" s="97"/>
       <c r="G26" s="44" t="s">
@@ -4073,11 +4065,11 @@
         <v>1</v>
       </c>
       <c r="I26" s="98" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J26" s="171"/>
       <c r="K26" s="172" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L26" s="100"/>
     </row>
@@ -4087,11 +4079,11 @@
         <v>2</v>
       </c>
       <c r="C27" s="98" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D27" s="171"/>
       <c r="E27" s="172" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F27" s="100"/>
       <c r="G27" s="45"/>
@@ -4103,7 +4095,7 @@
       </c>
       <c r="J27" s="86"/>
       <c r="K27" s="96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L27" s="97"/>
     </row>
@@ -4112,22 +4104,22 @@
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="215" t="s">
+      <c r="C28" s="213" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="216"/>
-      <c r="E28" s="216"/>
-      <c r="F28" s="217"/>
+      <c r="D28" s="214"/>
+      <c r="E28" s="214"/>
+      <c r="F28" s="215"/>
       <c r="G28" s="45"/>
       <c r="H28" s="26">
         <v>3</v>
       </c>
-      <c r="I28" s="215" t="s">
+      <c r="I28" s="213" t="s">
         <v>57</v>
       </c>
-      <c r="J28" s="216"/>
-      <c r="K28" s="216"/>
-      <c r="L28" s="217"/>
+      <c r="J28" s="214"/>
+      <c r="K28" s="214"/>
+      <c r="L28" s="215"/>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="36"/>
@@ -4137,37 +4129,37 @@
       <c r="C29" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="198"/>
-      <c r="E29" s="198"/>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
       <c r="F29" s="133"/>
       <c r="G29" s="46"/>
       <c r="H29" s="43">
         <v>4</v>
       </c>
-      <c r="I29" s="218" t="s">
+      <c r="I29" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="J29" s="219"/>
-      <c r="K29" s="219"/>
-      <c r="L29" s="220"/>
+      <c r="J29" s="217"/>
+      <c r="K29" s="217"/>
+      <c r="L29" s="218"/>
     </row>
     <row r="30" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="34"/>
       <c r="B30" s="30">
         <v>5</v>
       </c>
-      <c r="C30" s="199"/>
-      <c r="D30" s="200"/>
-      <c r="E30" s="200"/>
-      <c r="F30" s="201"/>
+      <c r="C30" s="197"/>
+      <c r="D30" s="198"/>
+      <c r="E30" s="198"/>
+      <c r="F30" s="199"/>
       <c r="G30" s="47"/>
       <c r="H30" s="30">
         <v>5</v>
       </c>
-      <c r="I30" s="225"/>
-      <c r="J30" s="226"/>
-      <c r="K30" s="226"/>
-      <c r="L30" s="227"/>
+      <c r="I30" s="223"/>
+      <c r="J30" s="224"/>
+      <c r="K30" s="224"/>
+      <c r="L30" s="225"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" s="48" t="s">
@@ -4176,9 +4168,7 @@
       <c r="B31" s="28">
         <v>1</v>
       </c>
-      <c r="C31" s="189" t="s">
-        <v>117</v>
-      </c>
+      <c r="C31" s="189"/>
       <c r="D31" s="190"/>
       <c r="E31" s="190"/>
       <c r="F31" s="191"/>
@@ -4188,9 +4178,7 @@
       <c r="H31" s="28">
         <v>1</v>
       </c>
-      <c r="I31" s="189" t="s">
-        <v>117</v>
-      </c>
+      <c r="I31" s="189"/>
       <c r="J31" s="190"/>
       <c r="K31" s="190"/>
       <c r="L31" s="191"/>
@@ -4201,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="95" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D32" s="96"/>
       <c r="E32" s="96"/>
@@ -4211,7 +4199,7 @@
         <v>2</v>
       </c>
       <c r="I32" s="98" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="J32" s="99"/>
       <c r="K32" s="99"/>
@@ -4222,22 +4210,22 @@
       <c r="B33" s="26">
         <v>3</v>
       </c>
-      <c r="C33" s="202"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203" t="s">
+      <c r="C33" s="200"/>
+      <c r="D33" s="201"/>
+      <c r="E33" s="201" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="204"/>
+      <c r="F33" s="202"/>
       <c r="G33" s="49"/>
       <c r="H33" s="26">
         <v>3</v>
       </c>
-      <c r="I33" s="221" t="s">
-        <v>100</v>
-      </c>
-      <c r="J33" s="222"/>
-      <c r="K33" s="223"/>
-      <c r="L33" s="224"/>
+      <c r="I33" s="219" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="220"/>
+      <c r="K33" s="221"/>
+      <c r="L33" s="222"/>
     </row>
     <row r="34" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="50"/>
@@ -4260,16 +4248,16 @@
     <row r="35" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="51"/>
       <c r="B35" s="52"/>
-      <c r="C35" s="212"/>
-      <c r="D35" s="213"/>
-      <c r="E35" s="213"/>
-      <c r="F35" s="214"/>
+      <c r="C35" s="210"/>
+      <c r="D35" s="211"/>
+      <c r="E35" s="211"/>
+      <c r="F35" s="212"/>
       <c r="G35" s="51"/>
       <c r="H35" s="52"/>
-      <c r="I35" s="212"/>
-      <c r="J35" s="213"/>
-      <c r="K35" s="213"/>
-      <c r="L35" s="214"/>
+      <c r="I35" s="210"/>
+      <c r="J35" s="211"/>
+      <c r="K35" s="211"/>
+      <c r="L35" s="212"/>
     </row>
     <row r="36" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="57"/>
@@ -4277,7 +4265,7 @@
         <v>30</v>
       </c>
       <c r="C36" s="189" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D36" s="190"/>
       <c r="E36" s="190"/>
@@ -4287,7 +4275,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="189" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J36" s="190"/>
       <c r="K36" s="190"/>
@@ -4299,20 +4287,20 @@
         <v>30</v>
       </c>
       <c r="C37" s="130" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" s="198"/>
-      <c r="E37" s="198"/>
+        <v>100</v>
+      </c>
+      <c r="D37" s="196"/>
+      <c r="E37" s="196"/>
       <c r="F37" s="133"/>
       <c r="G37" s="73"/>
       <c r="H37" s="75" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="130" t="s">
-        <v>101</v>
-      </c>
-      <c r="J37" s="198"/>
-      <c r="K37" s="198"/>
+        <v>100</v>
+      </c>
+      <c r="J37" s="196"/>
+      <c r="K37" s="196"/>
       <c r="L37" s="133"/>
     </row>
     <row r="38" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4321,7 +4309,7 @@
         <v>30</v>
       </c>
       <c r="C38" s="104" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D38" s="105"/>
       <c r="E38" s="105"/>
@@ -4331,7 +4319,7 @@
         <v>30</v>
       </c>
       <c r="I38" s="104" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J38" s="105"/>
       <c r="K38" s="105"/>
@@ -4342,22 +4330,22 @@
         <v>50</v>
       </c>
       <c r="B39" s="64"/>
-      <c r="C39" s="211" t="s">
+      <c r="C39" s="209" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="211"/>
-      <c r="E39" s="211"/>
-      <c r="F39" s="211"/>
+      <c r="D39" s="209"/>
+      <c r="E39" s="209"/>
+      <c r="F39" s="209"/>
       <c r="G39" s="63" t="s">
         <v>50</v>
       </c>
       <c r="H39" s="64"/>
-      <c r="I39" s="211" t="s">
+      <c r="I39" s="209" t="s">
         <v>56</v>
       </c>
-      <c r="J39" s="211"/>
-      <c r="K39" s="211"/>
-      <c r="L39" s="211"/>
+      <c r="J39" s="209"/>
+      <c r="K39" s="209"/>
+      <c r="L39" s="209"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
@@ -4388,18 +4376,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="77">
     <mergeCell ref="I21:L21"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I20:J20"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="I18:L18"/>
-    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="I20:L20"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="I25:L25"/>
@@ -4445,7 +4432,6 @@
     <mergeCell ref="I32:L32"/>
     <mergeCell ref="I31:L31"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="K20:L20"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F22"/>
@@ -4456,6 +4442,7 @@
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="I13:L13"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="I16:L16"/>
@@ -4563,7 +4550,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>69</v>
@@ -4573,7 +4560,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
       <c r="L4" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -4581,7 +4568,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -4594,7 +4581,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="10" t="s">
@@ -4654,7 +4641,7 @@
       </c>
       <c r="J7" s="134"/>
       <c r="K7" s="40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>7</v>
@@ -4665,7 +4652,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="135" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" s="135"/>
       <c r="E8" s="135"/>
@@ -4674,7 +4661,7 @@
         <v>26</v>
       </c>
       <c r="I8" s="135" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J8" s="135"/>
       <c r="K8" s="135"/>
@@ -4713,24 +4700,24 @@
       <c r="B10" s="24">
         <v>2</v>
       </c>
-      <c r="C10" s="262" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="263"/>
-      <c r="E10" s="264"/>
-      <c r="F10" s="265"/>
+      <c r="C10" s="257" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="258"/>
+      <c r="E10" s="259"/>
+      <c r="F10" s="260"/>
       <c r="G10" s="23" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="24">
         <v>3</v>
       </c>
-      <c r="I10" s="278" t="s">
-        <v>127</v>
-      </c>
-      <c r="J10" s="279"/>
-      <c r="K10" s="279"/>
-      <c r="L10" s="280"/>
+      <c r="I10" s="273" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="274"/>
+      <c r="K10" s="274"/>
+      <c r="L10" s="275"/>
     </row>
     <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="25"/>
@@ -4738,7 +4725,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D11" s="99"/>
       <c r="E11" s="99"/>
@@ -4748,7 +4735,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="98" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J11" s="99"/>
       <c r="K11" s="99"/>
@@ -4760,7 +4747,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="98" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D12" s="99"/>
       <c r="E12" s="99"/>
@@ -4770,7 +4757,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="98" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J12" s="99"/>
       <c r="K12" s="99"/>
@@ -4782,16 +4769,16 @@
         <v>6</v>
       </c>
       <c r="C13" s="168"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
       <c r="F13" s="188"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26">
         <v>6</v>
       </c>
       <c r="I13" s="168"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
       <c r="L13" s="188"/>
     </row>
     <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -4801,46 +4788,46 @@
       <c r="B14" s="28">
         <v>3</v>
       </c>
-      <c r="C14" s="256" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="257"/>
-      <c r="E14" s="257"/>
-      <c r="F14" s="258"/>
+      <c r="C14" s="251" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="252"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="253"/>
       <c r="G14" s="27" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="28">
         <v>3</v>
       </c>
-      <c r="I14" s="256" t="s">
-        <v>128</v>
-      </c>
-      <c r="J14" s="257"/>
-      <c r="K14" s="257"/>
-      <c r="L14" s="258"/>
+      <c r="I14" s="251" t="s">
+        <v>125</v>
+      </c>
+      <c r="J14" s="252"/>
+      <c r="K14" s="252"/>
+      <c r="L14" s="253"/>
     </row>
     <row r="15" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="25"/>
       <c r="B15" s="26">
         <v>4</v>
       </c>
-      <c r="C15" s="259" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="260"/>
-      <c r="E15" s="260"/>
-      <c r="F15" s="261"/>
+      <c r="C15" s="254" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="255"/>
+      <c r="E15" s="255"/>
+      <c r="F15" s="256"/>
       <c r="G15" s="25"/>
       <c r="H15" s="26">
         <v>4</v>
       </c>
-      <c r="I15" s="259" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="260"/>
-      <c r="K15" s="260"/>
-      <c r="L15" s="261"/>
+      <c r="I15" s="254" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="255"/>
+      <c r="K15" s="255"/>
+      <c r="L15" s="256"/>
     </row>
     <row r="16" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
@@ -4859,28 +4846,28 @@
       <c r="H16" s="26">
         <v>5</v>
       </c>
-      <c r="I16" s="281"/>
-      <c r="J16" s="282"/>
-      <c r="K16" s="282"/>
-      <c r="L16" s="283"/>
+      <c r="I16" s="276"/>
+      <c r="J16" s="277"/>
+      <c r="K16" s="277"/>
+      <c r="L16" s="278"/>
     </row>
     <row r="17" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="29"/>
       <c r="B17" s="30">
         <v>6</v>
       </c>
-      <c r="C17" s="253"/>
-      <c r="D17" s="254"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="255"/>
+      <c r="C17" s="248"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="250"/>
       <c r="G17" s="29"/>
       <c r="H17" s="30">
         <v>6</v>
       </c>
-      <c r="I17" s="253"/>
-      <c r="J17" s="254"/>
-      <c r="K17" s="254"/>
-      <c r="L17" s="255"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="249"/>
+      <c r="L17" s="250"/>
     </row>
     <row r="18" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="27" t="s">
@@ -4889,10 +4876,10 @@
       <c r="B18" s="28">
         <v>2</v>
       </c>
-      <c r="C18" s="266"/>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="268"/>
+      <c r="C18" s="261"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="263"/>
       <c r="G18" s="27" t="s">
         <v>22</v>
       </c>
@@ -4914,7 +4901,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="85" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D19" s="86"/>
       <c r="E19" s="86"/>
@@ -4939,10 +4926,10 @@
         <v>39</v>
       </c>
       <c r="D20" s="86"/>
-      <c r="E20" s="245" t="s">
+      <c r="E20" s="240" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="246"/>
+      <c r="F20" s="241"/>
       <c r="G20" s="42"/>
       <c r="H20" s="43">
         <v>4</v>
@@ -4960,7 +4947,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="85" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D21" s="86"/>
       <c r="E21" s="86"/>
@@ -4970,7 +4957,7 @@
         <v>5</v>
       </c>
       <c r="I21" s="85" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J21" s="86"/>
       <c r="K21" s="86"/>
@@ -4981,14 +4968,14 @@
       <c r="B22" s="30">
         <v>6</v>
       </c>
-      <c r="C22" s="247" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248" t="s">
-        <v>132</v>
-      </c>
-      <c r="F22" s="249"/>
+      <c r="C22" s="242" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="243"/>
+      <c r="E22" s="243" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="244"/>
       <c r="G22" s="29"/>
       <c r="H22" s="30">
         <v>6</v>
@@ -5026,7 +5013,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="98" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D24" s="99"/>
       <c r="E24" s="99"/>
@@ -5038,7 +5025,7 @@
       <c r="I24" s="113"/>
       <c r="J24" s="114"/>
       <c r="K24" s="114"/>
-      <c r="L24" s="277"/>
+      <c r="L24" s="272"/>
     </row>
     <row r="25" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
@@ -5046,7 +5033,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="95" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D25" s="96"/>
       <c r="E25" s="96"/>
@@ -5056,7 +5043,7 @@
         <v>3</v>
       </c>
       <c r="I25" s="95" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J25" s="96"/>
       <c r="K25" s="96"/>
@@ -5076,11 +5063,11 @@
         <v>4</v>
       </c>
       <c r="I26" s="95" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J26" s="96"/>
       <c r="K26" s="96" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L26" s="97"/>
     </row>
@@ -5089,22 +5076,22 @@
       <c r="B27" s="30">
         <v>5</v>
       </c>
-      <c r="C27" s="250"/>
-      <c r="D27" s="251"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="252"/>
+      <c r="C27" s="245"/>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="247"/>
       <c r="G27" s="29"/>
       <c r="H27" s="30">
         <v>5</v>
       </c>
-      <c r="I27" s="284" t="s">
-        <v>137</v>
-      </c>
-      <c r="J27" s="285"/>
-      <c r="K27" s="285" t="s">
-        <v>138</v>
-      </c>
-      <c r="L27" s="286"/>
+      <c r="I27" s="279" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="280"/>
+      <c r="K27" s="280" t="s">
+        <v>135</v>
+      </c>
+      <c r="L27" s="281"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="27" t="s">
@@ -5113,24 +5100,24 @@
       <c r="B28" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="205" t="s">
+      <c r="C28" s="203" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="206"/>
-      <c r="E28" s="206"/>
-      <c r="F28" s="207"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="204"/>
+      <c r="F28" s="205"/>
       <c r="G28" s="27" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="287" t="s">
+      <c r="I28" s="282" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="288"/>
-      <c r="K28" s="288"/>
-      <c r="L28" s="289"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="284"/>
     </row>
     <row r="29" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="33"/>
@@ -5140,7 +5127,7 @@
       <c r="C29" s="113"/>
       <c r="D29" s="114"/>
       <c r="E29" s="114"/>
-      <c r="F29" s="277"/>
+      <c r="F29" s="272"/>
       <c r="G29" s="33"/>
       <c r="H29" s="24">
         <v>4</v>
@@ -5159,46 +5146,46 @@
       <c r="B30" s="26">
         <v>5</v>
       </c>
-      <c r="C30" s="270" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="271"/>
-      <c r="E30" s="271"/>
-      <c r="F30" s="272"/>
+      <c r="C30" s="265" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="266"/>
+      <c r="E30" s="266"/>
+      <c r="F30" s="267"/>
       <c r="G30" s="33"/>
       <c r="H30" s="26">
         <v>5</v>
       </c>
-      <c r="I30" s="290" t="s">
+      <c r="I30" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="291"/>
-      <c r="K30" s="291"/>
-      <c r="L30" s="292"/>
+      <c r="J30" s="286"/>
+      <c r="K30" s="286"/>
+      <c r="L30" s="287"/>
     </row>
     <row r="31" spans="1:12" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="34"/>
       <c r="B31" s="30">
         <v>6</v>
       </c>
-      <c r="C31" s="273"/>
-      <c r="D31" s="274"/>
-      <c r="E31" s="275" t="s">
-        <v>140</v>
-      </c>
-      <c r="F31" s="276"/>
+      <c r="C31" s="268"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="270" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="271"/>
       <c r="G31" s="34"/>
       <c r="H31" s="30">
         <v>6</v>
       </c>
-      <c r="I31" s="293" t="s">
-        <v>135</v>
-      </c>
-      <c r="J31" s="294"/>
-      <c r="K31" s="294" t="s">
-        <v>136</v>
-      </c>
-      <c r="L31" s="295"/>
+      <c r="I31" s="288" t="s">
+        <v>132</v>
+      </c>
+      <c r="J31" s="289"/>
+      <c r="K31" s="289" t="s">
+        <v>133</v>
+      </c>
+      <c r="L31" s="290"/>
     </row>
     <row r="32" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="48" t="s">
@@ -5207,24 +5194,24 @@
       <c r="B32" s="28">
         <v>2</v>
       </c>
-      <c r="C32" s="240" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" s="241"/>
-      <c r="E32" s="241"/>
-      <c r="F32" s="242"/>
+      <c r="C32" s="235" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="236"/>
+      <c r="E32" s="236"/>
+      <c r="F32" s="237"/>
       <c r="G32" s="48" t="s">
         <v>25</v>
       </c>
       <c r="H32" s="28">
         <v>2</v>
       </c>
-      <c r="I32" s="194" t="s">
-        <v>141</v>
-      </c>
-      <c r="J32" s="243"/>
-      <c r="K32" s="243"/>
-      <c r="L32" s="197"/>
+      <c r="I32" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="J32" s="238"/>
+      <c r="K32" s="238"/>
+      <c r="L32" s="195"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="49"/>
@@ -5232,7 +5219,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="98" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D33" s="99"/>
       <c r="E33" s="99"/>
@@ -5242,7 +5229,7 @@
         <v>3</v>
       </c>
       <c r="I33" s="98" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J33" s="99"/>
       <c r="K33" s="99"/>
@@ -5254,7 +5241,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="98" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D34" s="99"/>
       <c r="E34" s="99"/>
@@ -5264,7 +5251,7 @@
         <v>4</v>
       </c>
       <c r="I34" s="98" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J34" s="99"/>
       <c r="K34" s="99"/>
@@ -5276,7 +5263,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="157" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D35" s="158"/>
       <c r="E35" s="158"/>
@@ -5286,7 +5273,7 @@
         <v>5</v>
       </c>
       <c r="I35" s="157" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J35" s="158"/>
       <c r="K35" s="158"/>
@@ -5297,22 +5284,22 @@
         <v>50</v>
       </c>
       <c r="B36" s="64"/>
-      <c r="C36" s="269" t="s">
+      <c r="C36" s="264" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="269"/>
-      <c r="E36" s="269"/>
-      <c r="F36" s="269"/>
+      <c r="D36" s="264"/>
+      <c r="E36" s="264"/>
+      <c r="F36" s="264"/>
       <c r="G36" s="63" t="s">
         <v>50</v>
       </c>
       <c r="H36" s="64"/>
-      <c r="I36" s="269" t="s">
+      <c r="I36" s="264" t="s">
         <v>53</v>
       </c>
-      <c r="J36" s="269"/>
-      <c r="K36" s="269"/>
-      <c r="L36" s="269"/>
+      <c r="J36" s="264"/>
+      <c r="K36" s="264"/>
+      <c r="L36" s="264"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
@@ -5484,7 +5471,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -5492,7 +5479,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -5547,7 +5534,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" s="53"/>
       <c r="E9" s="53"/>
@@ -5573,12 +5560,12 @@
       <c r="B11" s="24">
         <v>4</v>
       </c>
-      <c r="C11" s="205" t="s">
+      <c r="C11" s="203" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="206"/>
-      <c r="E11" s="206"/>
-      <c r="F11" s="207"/>
+      <c r="D11" s="204"/>
+      <c r="E11" s="204"/>
+      <c r="F11" s="205"/>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
@@ -5604,63 +5591,61 @@
       <c r="E13" s="96"/>
       <c r="F13" s="97"/>
     </row>
-    <row r="14" spans="1:6" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="41"/>
-      <c r="B14" s="30">
-        <v>7</v>
-      </c>
-      <c r="C14" s="110" t="s">
-        <v>151</v>
-      </c>
-      <c r="D14" s="111"/>
-      <c r="E14" s="163"/>
-      <c r="F14" s="164"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="162"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="28">
-        <v>3</v>
-      </c>
-      <c r="C15" s="297"/>
-      <c r="D15" s="298"/>
-      <c r="E15" s="298"/>
-      <c r="F15" s="299"/>
+        <v>4</v>
+      </c>
+      <c r="C15" s="292"/>
+      <c r="D15" s="293"/>
+      <c r="E15" s="293"/>
+      <c r="F15" s="294"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
-        <v>4</v>
-      </c>
-      <c r="C16" s="113"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="277"/>
+        <v>5</v>
+      </c>
+      <c r="C16" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="97"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="42"/>
       <c r="B17" s="43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="95" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" s="96"/>
       <c r="E17" s="96"/>
       <c r="F17" s="97"/>
     </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="30">
-        <v>6</v>
-      </c>
-      <c r="C18" s="300" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="301"/>
-      <c r="E18" s="301"/>
-      <c r="F18" s="302"/>
+        <v>7</v>
+      </c>
+      <c r="C18" s="279" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="280"/>
+      <c r="E18" s="280"/>
+      <c r="F18" s="281"/>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="23" t="s">
@@ -5669,7 +5654,7 @@
       <c r="B19" s="24">
         <v>3</v>
       </c>
-      <c r="C19" s="296"/>
+      <c r="C19" s="291"/>
       <c r="D19" s="90"/>
       <c r="E19" s="90"/>
       <c r="F19" s="91"/>
@@ -5717,12 +5702,12 @@
       <c r="B23" s="28">
         <v>3</v>
       </c>
-      <c r="C23" s="194" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="243"/>
-      <c r="E23" s="243"/>
-      <c r="F23" s="197"/>
+      <c r="C23" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="238"/>
+      <c r="E23" s="238"/>
+      <c r="F23" s="195"/>
     </row>
     <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
@@ -5730,7 +5715,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="95" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D24" s="96"/>
       <c r="E24" s="96"/>
@@ -5742,7 +5727,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="98" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D25" s="99"/>
       <c r="E25" s="99"/>
@@ -5754,7 +5739,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="160" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D26" s="161"/>
       <c r="E26" s="161"/>
@@ -5768,7 +5753,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="154" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D27" s="155"/>
       <c r="E27" s="155"/>
@@ -5780,7 +5765,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="98" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D28" s="99"/>
       <c r="E28" s="99"/>
@@ -5792,7 +5777,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="98" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D29" s="99"/>
       <c r="E29" s="99"/>
@@ -5816,11 +5801,11 @@
         <v>1</v>
       </c>
       <c r="C31" s="154" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D31" s="155"/>
-      <c r="E31" s="267"/>
-      <c r="F31" s="268"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="263"/>
     </row>
     <row r="32" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="49"/>
@@ -5828,11 +5813,11 @@
         <v>2</v>
       </c>
       <c r="C32" s="95" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D32" s="96"/>
       <c r="E32" s="96" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F32" s="97"/>
     </row>
@@ -5844,7 +5829,7 @@
       <c r="C33" s="95"/>
       <c r="D33" s="96"/>
       <c r="E33" s="96" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F33" s="97"/>
     </row>
@@ -5879,10 +5864,10 @@
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C14:F14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="C12:F12"/>
